--- a/artfynd/A 22607-2025 artfynd.xlsx
+++ b/artfynd/A 22607-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74574646</v>
       </c>
       <c r="B2" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484521.5091085946</v>
+        <v>484522</v>
       </c>
       <c r="R2" t="n">
-        <v>6263802.874828933</v>
+        <v>6263803</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74702204</v>
       </c>
       <c r="B3" t="n">
-        <v>104541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484521.5091085946</v>
+        <v>484522</v>
       </c>
       <c r="R3" t="n">
-        <v>6263802.874828933</v>
+        <v>6263803</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1991-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74840816</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484521.5091085946</v>
+        <v>484522</v>
       </c>
       <c r="R4" t="n">
-        <v>6263802.874828933</v>
+        <v>6263803</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 22607-2025 artfynd.xlsx
+++ b/artfynd/A 22607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574646</v>
       </c>
       <c r="B2" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74702204</v>
       </c>
       <c r="B3" t="n">
-        <v>107042</v>
+        <v>107051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74840816</v>
       </c>
       <c r="B4" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22607-2025 artfynd.xlsx
+++ b/artfynd/A 22607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574646</v>
       </c>
       <c r="B2" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74702204</v>
       </c>
       <c r="B3" t="n">
-        <v>107051</v>
+        <v>107056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74840816</v>
       </c>
       <c r="B4" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22607-2025 artfynd.xlsx
+++ b/artfynd/A 22607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574646</v>
       </c>
       <c r="B2" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74702204</v>
       </c>
       <c r="B3" t="n">
-        <v>107056</v>
+        <v>107084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74840816</v>
       </c>
       <c r="B4" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22607-2025 artfynd.xlsx
+++ b/artfynd/A 22607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574646</v>
       </c>
       <c r="B2" t="n">
-        <v>109265</v>
+        <v>109271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74702204</v>
       </c>
       <c r="B3" t="n">
-        <v>107084</v>
+        <v>107090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74840816</v>
       </c>
       <c r="B4" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22607-2025 artfynd.xlsx
+++ b/artfynd/A 22607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574646</v>
       </c>
       <c r="B2" t="n">
-        <v>109271</v>
+        <v>109278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74702204</v>
       </c>
       <c r="B3" t="n">
-        <v>107090</v>
+        <v>107097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74840816</v>
       </c>
       <c r="B4" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22607-2025 artfynd.xlsx
+++ b/artfynd/A 22607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574646</v>
       </c>
       <c r="B2" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74702204</v>
       </c>
       <c r="B3" t="n">
-        <v>107097</v>
+        <v>107101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74840816</v>
       </c>
       <c r="B4" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22607-2025 artfynd.xlsx
+++ b/artfynd/A 22607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574646</v>
       </c>
       <c r="B2" t="n">
-        <v>109282</v>
+        <v>109290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74702204</v>
       </c>
       <c r="B3" t="n">
-        <v>107101</v>
+        <v>107109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74840816</v>
       </c>
       <c r="B4" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
